--- a/artfynd/A 47047-2024 artfynd.xlsx
+++ b/artfynd/A 47047-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120729309</v>
+        <v>120755112</v>
       </c>
       <c r="B2" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sompasenvuoma, Nb</t>
+          <t>Kuijumaa, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>885447</v>
+        <v>885427</v>
       </c>
       <c r="R2" t="n">
-        <v>7404196</v>
+        <v>7404232</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -753,6 +748,11 @@
           <t>2024-10-28</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>15 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -765,27 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120729308</v>
+        <v>120755093</v>
       </c>
       <c r="B3" t="n">
-        <v>79706</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sompasenvuoma, Nb</t>
+          <t>Kuijumaa, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>885464</v>
+        <v>885403</v>
       </c>
       <c r="R3" t="n">
-        <v>7404217</v>
+        <v>7404240</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -867,49 +862,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120729313</v>
+        <v>120729306</v>
       </c>
       <c r="B4" t="n">
-        <v>90700</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>885438</v>
+        <v>885441</v>
       </c>
       <c r="R4" t="n">
-        <v>7404149</v>
+        <v>7404156</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,50 +971,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120729306</v>
+        <v>120755120</v>
       </c>
       <c r="B5" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sompasenvuoma, Nb</t>
+          <t>Kuijumaa, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>885441</v>
+        <v>885510</v>
       </c>
       <c r="R5" t="n">
-        <v>7404156</v>
+        <v>7404153</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1071,62 +1056,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120729307</v>
+        <v>120755123</v>
       </c>
       <c r="B6" t="n">
-        <v>79706</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sompasenvuoma, Nb</t>
+          <t>Kuijumaa, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>885429</v>
+        <v>885503</v>
       </c>
       <c r="R6" t="n">
-        <v>7404144</v>
+        <v>7404228</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1173,27 +1153,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120729311</v>
+        <v>120755124</v>
       </c>
       <c r="B7" t="n">
-        <v>98059</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,34 +1176,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sompasenvuoma, Nb</t>
+          <t>Kuijumaa, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>885428</v>
+        <v>885495</v>
       </c>
       <c r="R7" t="n">
-        <v>7404145</v>
+        <v>7404244</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1275,27 +1250,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120729312</v>
+        <v>120729309</v>
       </c>
       <c r="B8" t="n">
-        <v>90700</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>885450</v>
+        <v>885447</v>
       </c>
       <c r="R8" t="n">
-        <v>7404197</v>
+        <v>7404196</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1389,37 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120755117</v>
+        <v>120755115</v>
       </c>
       <c r="B9" t="n">
-        <v>98059</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>885459</v>
+        <v>885477</v>
       </c>
       <c r="R9" t="n">
-        <v>7404218</v>
+        <v>7404142</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1491,37 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120755098</v>
+        <v>120755116</v>
       </c>
       <c r="B10" t="n">
-        <v>79706</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>885507</v>
+        <v>885453</v>
       </c>
       <c r="R10" t="n">
-        <v>7404151</v>
+        <v>7404210</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,50 +1553,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120755116</v>
+        <v>120729307</v>
       </c>
       <c r="B11" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kuijumaa, Nb</t>
+          <t>Sompasenvuoma, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>885453</v>
+        <v>885429</v>
       </c>
       <c r="R11" t="n">
-        <v>7404210</v>
+        <v>7404144</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1683,62 +1638,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120755115</v>
+        <v>120729308</v>
       </c>
       <c r="B12" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kuijumaa, Nb</t>
+          <t>Sompasenvuoma, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>885477</v>
+        <v>885464</v>
       </c>
       <c r="R12" t="n">
-        <v>7404142</v>
+        <v>7404217</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1785,27 +1735,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120755100</v>
+        <v>120755098</v>
       </c>
       <c r="B13" t="n">
-        <v>79706</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1837,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>885454</v>
+        <v>885507</v>
       </c>
       <c r="R13" t="n">
-        <v>7404224</v>
+        <v>7404151</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1899,15 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120755101</v>
+        <v>120755099</v>
       </c>
       <c r="B14" t="n">
-        <v>79706</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>885458</v>
+        <v>885504</v>
       </c>
       <c r="R14" t="n">
-        <v>7404217</v>
+        <v>7404172</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2001,15 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120755099</v>
+        <v>120755100</v>
       </c>
       <c r="B15" t="n">
-        <v>79706</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>885504</v>
+        <v>885454</v>
       </c>
       <c r="R15" t="n">
-        <v>7404172</v>
+        <v>7404224</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2103,37 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120755120</v>
+        <v>120755101</v>
       </c>
       <c r="B16" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>885510</v>
+        <v>885458</v>
       </c>
       <c r="R16" t="n">
-        <v>7404153</v>
+        <v>7404217</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2202,6 +2132,399 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120755102</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kuijumaa, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>885424</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7404231</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120755097</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kuijumaa, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>885408</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7404251</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>avbarkad gran</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120729311</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sompasenvuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>885428</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7404145</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120755117</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kuijumaa, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>885459</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7404218</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47047-2024 artfynd.xlsx
+++ b/artfynd/A 47047-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755112</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755093</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729306</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755120</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755123</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755124</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729309</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755115</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755116</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729307</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729308</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755098</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755099</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755100</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755101</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,6 +2309,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755102</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2331,6 +2416,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755097</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2428,6 +2518,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729311</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2525,8 +2620,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755117</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>